--- a/ConfigExporter/xlsx/scene.xlsx
+++ b/ConfigExporter/xlsx/scene.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Project\WeiqiXN\ConfigExporter\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61EC8309-4A2F-411F-8CDA-29E62FD594F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DE9EFCC-4EB0-4746-B0D2-621E7B0B716B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6135" yWindow="5775" windowWidth="29205" windowHeight="13680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5580" yWindow="2715" windowWidth="29205" windowHeight="13680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="scene" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="11">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -63,7 +63,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>#require#enum(MainMenu)</t>
+    <t>Duel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#require#enum(MainMenu,Duel)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -426,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.625" style="1" customWidth="1"/>
@@ -467,7 +471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" s="6" customFormat="1" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
@@ -475,7 +479,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -487,6 +491,17 @@
       </c>
       <c r="C5" s="4" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
